--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -667,15 +667,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B13"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="23" min="1" max="1"/>
     <col width="108" customWidth="1" style="23" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="24">
       <c r="B2" s="25" t="inlineStr">
         <is>
@@ -690,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="24">
       <c r="B5" s="27" t="inlineStr">
         <is>
@@ -718,6 +720,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1" s="24">
       <c r="B10" s="27" t="inlineStr">
         <is>
@@ -732,6 +735,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="25.5" customHeight="1" s="24">
       <c r="B13" s="29" t="inlineStr">
         <is>
@@ -739,10 +743,37 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -750,7 +781,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1708,8 +1739,8 @@
       <formula2>0.5</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -152,7 +153,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -206,6 +207,11 @@
         <fgColor rgb="FFFFF9E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -241,7 +247,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -386,6 +392,7 @@
     <xf numFmtId="164" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,6 +493,185 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>p-value by test, against alpha = 0.05</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>p-value</v>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Test log'!$A$11:$A$35</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Test log'!$J$11:$J$35</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>alpha (0.05)</v>
+          </tx>
+          <spPr>
+            <a:ln w="16000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Test log'!$A$11:$A$35</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Test log'!$T$11:$T$35</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>p-value</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.000" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -783,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="23" min="1" max="1"/>
@@ -963,6 +1149,11 @@
           <t>Analyst</t>
         </is>
       </c>
+      <c r="T10" s="37" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="348.5" customHeight="1" s="24">
       <c r="A11" s="41" t="n">
@@ -1043,6 +1234,10 @@
         <is>
           <t>M. Berenji</t>
         </is>
+      </c>
+      <c r="T11" s="50">
+        <f>IF(J11="","",0.05)</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="24">
@@ -1069,6 +1264,10 @@
       <c r="P12" s="47" t="n"/>
       <c r="Q12" s="47" t="n"/>
       <c r="R12" s="47" t="n"/>
+      <c r="T12" s="50">
+        <f>IF(J12="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="24">
       <c r="A13" s="46" t="n">
@@ -1094,6 +1293,10 @@
       <c r="P13" s="47" t="n"/>
       <c r="Q13" s="47" t="n"/>
       <c r="R13" s="47" t="n"/>
+      <c r="T13" s="50">
+        <f>IF(J13="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="24">
       <c r="A14" s="46" t="n">
@@ -1119,6 +1322,10 @@
       <c r="P14" s="47" t="n"/>
       <c r="Q14" s="47" t="n"/>
       <c r="R14" s="47" t="n"/>
+      <c r="T14" s="50">
+        <f>IF(J14="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="24">
       <c r="A15" s="46" t="n">
@@ -1144,6 +1351,10 @@
       <c r="P15" s="47" t="n"/>
       <c r="Q15" s="47" t="n"/>
       <c r="R15" s="47" t="n"/>
+      <c r="T15" s="50">
+        <f>IF(J15="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="24">
       <c r="A16" s="46" t="n">
@@ -1169,6 +1380,10 @@
       <c r="P16" s="47" t="n"/>
       <c r="Q16" s="47" t="n"/>
       <c r="R16" s="47" t="n"/>
+      <c r="T16" s="50">
+        <f>IF(J16="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="24">
       <c r="A17" s="46" t="n">
@@ -1194,6 +1409,10 @@
       <c r="P17" s="47" t="n"/>
       <c r="Q17" s="47" t="n"/>
       <c r="R17" s="47" t="n"/>
+      <c r="T17" s="50">
+        <f>IF(J17="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="24">
       <c r="A18" s="46" t="n">
@@ -1219,6 +1438,10 @@
       <c r="P18" s="47" t="n"/>
       <c r="Q18" s="47" t="n"/>
       <c r="R18" s="47" t="n"/>
+      <c r="T18" s="50">
+        <f>IF(J18="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="24">
       <c r="A19" s="46" t="n">
@@ -1244,6 +1467,10 @@
       <c r="P19" s="47" t="n"/>
       <c r="Q19" s="47" t="n"/>
       <c r="R19" s="47" t="n"/>
+      <c r="T19" s="50">
+        <f>IF(J19="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="24">
       <c r="A20" s="46" t="n">
@@ -1269,6 +1496,10 @@
       <c r="P20" s="47" t="n"/>
       <c r="Q20" s="47" t="n"/>
       <c r="R20" s="47" t="n"/>
+      <c r="T20" s="50">
+        <f>IF(J20="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="24">
       <c r="A21" s="46" t="n">
@@ -1294,6 +1525,10 @@
       <c r="P21" s="47" t="n"/>
       <c r="Q21" s="47" t="n"/>
       <c r="R21" s="47" t="n"/>
+      <c r="T21" s="50">
+        <f>IF(J21="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="24">
       <c r="A22" s="46" t="n">
@@ -1319,6 +1554,10 @@
       <c r="P22" s="47" t="n"/>
       <c r="Q22" s="47" t="n"/>
       <c r="R22" s="47" t="n"/>
+      <c r="T22" s="50">
+        <f>IF(J22="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="24">
       <c r="A23" s="46" t="n">
@@ -1344,6 +1583,10 @@
       <c r="P23" s="47" t="n"/>
       <c r="Q23" s="47" t="n"/>
       <c r="R23" s="47" t="n"/>
+      <c r="T23" s="50">
+        <f>IF(J23="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="24">
       <c r="A24" s="46" t="n">
@@ -1369,6 +1612,10 @@
       <c r="P24" s="47" t="n"/>
       <c r="Q24" s="47" t="n"/>
       <c r="R24" s="47" t="n"/>
+      <c r="T24" s="50">
+        <f>IF(J24="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="24">
       <c r="A25" s="46" t="n">
@@ -1394,6 +1641,10 @@
       <c r="P25" s="47" t="n"/>
       <c r="Q25" s="47" t="n"/>
       <c r="R25" s="47" t="n"/>
+      <c r="T25" s="50">
+        <f>IF(J25="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="24">
       <c r="A26" s="46" t="n">
@@ -1419,6 +1670,10 @@
       <c r="P26" s="47" t="n"/>
       <c r="Q26" s="47" t="n"/>
       <c r="R26" s="47" t="n"/>
+      <c r="T26" s="50">
+        <f>IF(J26="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="24">
       <c r="A27" s="46" t="n">
@@ -1444,6 +1699,10 @@
       <c r="P27" s="47" t="n"/>
       <c r="Q27" s="47" t="n"/>
       <c r="R27" s="47" t="n"/>
+      <c r="T27" s="50">
+        <f>IF(J27="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="24">
       <c r="A28" s="46" t="n">
@@ -1469,6 +1728,10 @@
       <c r="P28" s="47" t="n"/>
       <c r="Q28" s="47" t="n"/>
       <c r="R28" s="47" t="n"/>
+      <c r="T28" s="50">
+        <f>IF(J28="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="24">
       <c r="A29" s="46" t="n">
@@ -1494,6 +1757,10 @@
       <c r="P29" s="47" t="n"/>
       <c r="Q29" s="47" t="n"/>
       <c r="R29" s="47" t="n"/>
+      <c r="T29" s="50">
+        <f>IF(J29="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="24">
       <c r="A30" s="46" t="n">
@@ -1519,6 +1786,10 @@
       <c r="P30" s="47" t="n"/>
       <c r="Q30" s="47" t="n"/>
       <c r="R30" s="47" t="n"/>
+      <c r="T30" s="50">
+        <f>IF(J30="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="24">
       <c r="A31" s="46" t="n">
@@ -1544,6 +1815,10 @@
       <c r="P31" s="47" t="n"/>
       <c r="Q31" s="47" t="n"/>
       <c r="R31" s="47" t="n"/>
+      <c r="T31" s="50">
+        <f>IF(J31="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="24">
       <c r="A32" s="46" t="n">
@@ -1569,6 +1844,10 @@
       <c r="P32" s="47" t="n"/>
       <c r="Q32" s="47" t="n"/>
       <c r="R32" s="47" t="n"/>
+      <c r="T32" s="50">
+        <f>IF(J32="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="24">
       <c r="A33" s="46" t="n">
@@ -1594,6 +1873,22 @@
       <c r="P33" s="47" t="n"/>
       <c r="Q33" s="47" t="n"/>
       <c r="R33" s="47" t="n"/>
+      <c r="T33" s="50">
+        <f>IF(J33="","",0.05)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="T34" s="50">
+        <f>IF(J34="","",0.05)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="T35" s="50">
+        <f>IF(J35="","",0.05)</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="24">
       <c r="A36" s="32" t="inlineStr">
@@ -1742,5 +2037,6 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -153,7 +153,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -212,6 +212,11 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -247,7 +252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -393,6 +398,27 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1156,57 +1182,57 @@
       </c>
     </row>
     <row r="11" ht="348.5" customHeight="1" s="24">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="42" t="inlineStr">
-        <is>
-          <t>Did the deferred-close rule reduce 7-day reopens?</t>
-        </is>
-      </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>Did the deferred-close rule cut reopens?</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr">
         <is>
           <t>2-proportion test</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="52" t="inlineStr">
         <is>
           <t>Proportion</t>
         </is>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E11" s="52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="42" t="inlineStr">
-        <is>
-          <t>Contact reason, tenure band</t>
-        </is>
-      </c>
-      <c r="G11" s="43" t="n">
+      <c r="F11" s="52" t="inlineStr">
+        <is>
+          <t>Contact reason, tenure</t>
+        </is>
+      </c>
+      <c r="G11" s="53" t="n">
         <v>0.41</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="52" t="n">
         <v>7420</v>
       </c>
-      <c r="I11" s="42" t="n">
+      <c r="I11" s="52" t="n">
         <v>7180</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="54" t="n">
         <v>0.0001</v>
       </c>
-      <c r="K11" s="42" t="inlineStr">
+      <c r="K11" s="52" t="inlineStr">
         <is>
           <t>-4.9 pts</t>
         </is>
       </c>
-      <c r="L11" s="42" t="inlineStr">
+      <c r="L11" s="52" t="inlineStr">
         <is>
           <t>-6.1 to -3.7</t>
         </is>
       </c>
-      <c r="M11" s="42" t="inlineStr">
+      <c r="M11" s="52" t="inlineStr">
         <is>
           <t>1.5 pts</t>
         </is>
@@ -1215,22 +1241,22 @@
         <f>IF(OR(J11="",K11="",M11=""),"",IF(J11&gt;$B$8,"NOT SIGNIFICANT",IF(ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(K11,"pts",""),"%","")),0))&gt;=ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(M11,"pts",""),"%","")),0)),"YES — real and matters","NO — significant but too small")))</f>
         <v/>
       </c>
-      <c r="O11" s="42" t="inlineStr">
-        <is>
-          <t>Reopens fell 4.9 points in the treatment pods versus a matched control. Well above the 1.5-point threshold.</t>
-        </is>
-      </c>
-      <c r="P11" s="42" t="inlineStr">
+      <c r="O11" s="52" t="inlineStr">
+        <is>
+          <t>Reopens fell 4.9 points, well past the 1.5 we agreed mattered</t>
+        </is>
+      </c>
+      <c r="P11" s="52" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="Q11" s="42" t="inlineStr">
+      <c r="Q11" s="52" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="R11" s="42" t="inlineStr">
+      <c r="R11" s="52" t="inlineStr">
         <is>
           <t>M. Berenji</t>
         </is>
@@ -1241,116 +1267,340 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="24">
-      <c r="A12" s="46" t="n">
+      <c r="A12" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="47" t="n"/>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
-      <c r="E12" s="47" t="n"/>
-      <c r="F12" s="47" t="n"/>
-      <c r="G12" s="48" t="n"/>
-      <c r="H12" s="47" t="n"/>
-      <c r="I12" s="47" t="n"/>
-      <c r="J12" s="49" t="n"/>
-      <c r="K12" s="47" t="n"/>
-      <c r="L12" s="47" t="n"/>
-      <c r="M12" s="47" t="n"/>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>Did the shorter code list improve routing accuracy?</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>2-proportion test</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>Proportion</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>Queue, tenure</t>
+        </is>
+      </c>
+      <c r="G12" s="56" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H12" s="55" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I12" s="55" t="n">
+        <v>4260</v>
+      </c>
+      <c r="J12" s="57" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="K12" s="55" t="inlineStr">
+        <is>
+          <t>+6.2 pts</t>
+        </is>
+      </c>
+      <c r="L12" s="55" t="inlineStr">
+        <is>
+          <t>+2.1 to +10.3</t>
+        </is>
+      </c>
+      <c r="M12" s="55" t="inlineStr">
+        <is>
+          <t>3.0 pts</t>
+        </is>
+      </c>
       <c r="N12" s="45">
         <f>IF(OR(J12="",K12="",M12=""),"",IF(J12&gt;$B$8,"NOT SIGNIFICANT",IF(ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(K12,"pts",""),"%","")),0))&gt;=ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(M12,"pts",""),"%","")),0)),"YES — real and matters","NO — significant but too small")))</f>
         <v/>
       </c>
-      <c r="O12" s="47" t="n"/>
-      <c r="P12" s="47" t="n"/>
-      <c r="Q12" s="47" t="n"/>
-      <c r="R12" s="47" t="n"/>
+      <c r="O12" s="55" t="inlineStr">
+        <is>
+          <t>Routing accuracy up 6.2 points</t>
+        </is>
+      </c>
+      <c r="P12" s="55" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="Q12" s="55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="R12" s="55" t="inlineStr">
+        <is>
+          <t>M. Berenji</t>
+        </is>
+      </c>
       <c r="T12" s="50">
         <f>IF(J12="","",0.05)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="24">
-      <c r="A13" s="46" t="n">
+      <c r="A13" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="47" t="n"/>
-      <c r="C13" s="47" t="n"/>
-      <c r="D13" s="47" t="n"/>
-      <c r="E13" s="47" t="n"/>
-      <c r="F13" s="47" t="n"/>
-      <c r="G13" s="48" t="n"/>
-      <c r="H13" s="47" t="n"/>
-      <c r="I13" s="47" t="n"/>
-      <c r="J13" s="49" t="n"/>
-      <c r="K13" s="47" t="n"/>
-      <c r="L13" s="47" t="n"/>
-      <c r="M13" s="47" t="n"/>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>Is handle time different across the three sites?</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>One-way ANOVA</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>Contact reason</t>
+        </is>
+      </c>
+      <c r="G13" s="56" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H13" s="55" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I13" s="55" t="n">
+        <v>5150</v>
+      </c>
+      <c r="J13" s="57" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K13" s="55" t="inlineStr">
+        <is>
+          <t>0.4 min</t>
+        </is>
+      </c>
+      <c r="L13" s="55" t="inlineStr">
+        <is>
+          <t>-0.3 to 1.1</t>
+        </is>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>1.0 min</t>
+        </is>
+      </c>
       <c r="N13" s="45">
         <f>IF(OR(J13="",K13="",M13=""),"",IF(J13&gt;$B$8,"NOT SIGNIFICANT",IF(ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(K13,"pts",""),"%","")),0))&gt;=ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(M13,"pts",""),"%","")),0)),"YES — real and matters","NO — significant but too small")))</f>
         <v/>
       </c>
-      <c r="O13" s="47" t="n"/>
-      <c r="P13" s="47" t="n"/>
-      <c r="Q13" s="47" t="n"/>
-      <c r="R13" s="47" t="n"/>
+      <c r="O13" s="55" t="inlineStr">
+        <is>
+          <t>No detectable site difference once contact mix is held constant</t>
+        </is>
+      </c>
+      <c r="P13" s="55" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="Q13" s="55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="R13" s="55" t="inlineStr">
+        <is>
+          <t>A. Okafor</t>
+        </is>
+      </c>
       <c r="T13" s="50">
         <f>IF(J13="","",0.05)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="24">
-      <c r="A14" s="46" t="n">
+      <c r="A14" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="47" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="E14" s="47" t="n"/>
-      <c r="F14" s="47" t="n"/>
-      <c r="G14" s="48" t="n"/>
-      <c r="H14" s="47" t="n"/>
-      <c r="I14" s="47" t="n"/>
-      <c r="J14" s="49" t="n"/>
-      <c r="K14" s="47" t="n"/>
-      <c r="L14" s="47" t="n"/>
-      <c r="M14" s="47" t="n"/>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>Did the 48-hour reminder reduce auto-closes?</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>2-proportion test</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>Proportion</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>Contact reason</t>
+        </is>
+      </c>
+      <c r="G14" s="56" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H14" s="55" t="n">
+        <v>3900</v>
+      </c>
+      <c r="I14" s="55" t="n">
+        <v>3880</v>
+      </c>
+      <c r="J14" s="57" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="K14" s="55" t="inlineStr">
+        <is>
+          <t>-3.1 pts</t>
+        </is>
+      </c>
+      <c r="L14" s="55" t="inlineStr">
+        <is>
+          <t>-4.8 to -1.4</t>
+        </is>
+      </c>
+      <c r="M14" s="55" t="inlineStr">
+        <is>
+          <t>2.0 pts</t>
+        </is>
+      </c>
       <c r="N14" s="45">
         <f>IF(OR(J14="",K14="",M14=""),"",IF(J14&gt;$B$8,"NOT SIGNIFICANT",IF(ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(K14,"pts",""),"%","")),0))&gt;=ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(M14,"pts",""),"%","")),0)),"YES — real and matters","NO — significant but too small")))</f>
         <v/>
       </c>
-      <c r="O14" s="47" t="n"/>
-      <c r="P14" s="47" t="n"/>
-      <c r="Q14" s="47" t="n"/>
-      <c r="R14" s="47" t="n"/>
+      <c r="O14" s="55" t="inlineStr">
+        <is>
+          <t>Auto-closes down 3.1 points</t>
+        </is>
+      </c>
+      <c r="P14" s="55" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="Q14" s="55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="R14" s="55" t="inlineStr">
+        <is>
+          <t>A. Okafor</t>
+        </is>
+      </c>
       <c r="T14" s="50">
         <f>IF(J14="","",0.05)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="24">
-      <c r="A15" s="46" t="n">
+      <c r="A15" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="47" t="n"/>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="47" t="n"/>
-      <c r="F15" s="47" t="n"/>
-      <c r="G15" s="48" t="n"/>
-      <c r="H15" s="47" t="n"/>
-      <c r="I15" s="47" t="n"/>
-      <c r="J15" s="49" t="n"/>
-      <c r="K15" s="47" t="n"/>
-      <c r="L15" s="47" t="n"/>
-      <c r="M15" s="47" t="n"/>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Does tenure predict QA score?</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>Simple regression</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>Queue</t>
+        </is>
+      </c>
+      <c r="G15" s="56" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H15" s="55" t="n">
+        <v>840</v>
+      </c>
+      <c r="I15" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="57" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K15" s="55" t="inlineStr">
+        <is>
+          <t>R-sq 0.09</t>
+        </is>
+      </c>
+      <c r="L15" s="55" t="inlineStr">
+        <is>
+          <t>slope 0.02 to 0.31</t>
+        </is>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>R-sq 0.25</t>
+        </is>
+      </c>
       <c r="N15" s="45">
         <f>IF(OR(J15="",K15="",M15=""),"",IF(J15&gt;$B$8,"NOT SIGNIFICANT",IF(ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(K15,"pts",""),"%","")),0))&gt;=ABS(IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(M15,"pts",""),"%","")),0)),"YES — real and matters","NO — significant but too small")))</f>
         <v/>
       </c>
-      <c r="O15" s="47" t="n"/>
-      <c r="P15" s="47" t="n"/>
-      <c r="Q15" s="47" t="n"/>
-      <c r="R15" s="47" t="n"/>
+      <c r="O15" s="55" t="inlineStr">
+        <is>
+          <t>Significant but explains only 9% — statistically real, operationally thin</t>
+        </is>
+      </c>
+      <c r="P15" s="55" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="Q15" s="55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R15" s="55" t="inlineStr">
+        <is>
+          <t>M. Berenji</t>
+        </is>
+      </c>
       <c r="T15" s="50">
         <f>IF(J15="","",0.05)</f>
         <v/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="T11" s="50">
-        <f>IF(J11="","",0.05)</f>
+        <f>IF(A11="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="T12" s="50">
-        <f>IF(J12="","",0.05)</f>
+        <f>IF(A12="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="T13" s="50">
-        <f>IF(J13="","",0.05)</f>
+        <f>IF(A13="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="T14" s="50">
-        <f>IF(J14="","",0.05)</f>
+        <f>IF(A14="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="T15" s="50">
-        <f>IF(J15="","",0.05)</f>
+        <f>IF(A15="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       <c r="Q16" s="47" t="n"/>
       <c r="R16" s="47" t="n"/>
       <c r="T16" s="50">
-        <f>IF(J16="","",0.05)</f>
+        <f>IF(A16="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       <c r="Q17" s="47" t="n"/>
       <c r="R17" s="47" t="n"/>
       <c r="T17" s="50">
-        <f>IF(J17="","",0.05)</f>
+        <f>IF(A17="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       <c r="Q18" s="47" t="n"/>
       <c r="R18" s="47" t="n"/>
       <c r="T18" s="50">
-        <f>IF(J18="","",0.05)</f>
+        <f>IF(A18="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       <c r="Q19" s="47" t="n"/>
       <c r="R19" s="47" t="n"/>
       <c r="T19" s="50">
-        <f>IF(J19="","",0.05)</f>
+        <f>IF(A19="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       <c r="Q20" s="47" t="n"/>
       <c r="R20" s="47" t="n"/>
       <c r="T20" s="50">
-        <f>IF(J20="","",0.05)</f>
+        <f>IF(A20="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       <c r="Q21" s="47" t="n"/>
       <c r="R21" s="47" t="n"/>
       <c r="T21" s="50">
-        <f>IF(J21="","",0.05)</f>
+        <f>IF(A21="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       <c r="Q22" s="47" t="n"/>
       <c r="R22" s="47" t="n"/>
       <c r="T22" s="50">
-        <f>IF(J22="","",0.05)</f>
+        <f>IF(A22="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       <c r="Q23" s="47" t="n"/>
       <c r="R23" s="47" t="n"/>
       <c r="T23" s="50">
-        <f>IF(J23="","",0.05)</f>
+        <f>IF(A23="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       <c r="Q24" s="47" t="n"/>
       <c r="R24" s="47" t="n"/>
       <c r="T24" s="50">
-        <f>IF(J24="","",0.05)</f>
+        <f>IF(A24="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       <c r="Q25" s="47" t="n"/>
       <c r="R25" s="47" t="n"/>
       <c r="T25" s="50">
-        <f>IF(J25="","",0.05)</f>
+        <f>IF(A25="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       <c r="Q26" s="47" t="n"/>
       <c r="R26" s="47" t="n"/>
       <c r="T26" s="50">
-        <f>IF(J26="","",0.05)</f>
+        <f>IF(A26="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       <c r="Q27" s="47" t="n"/>
       <c r="R27" s="47" t="n"/>
       <c r="T27" s="50">
-        <f>IF(J27="","",0.05)</f>
+        <f>IF(A27="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       <c r="Q28" s="47" t="n"/>
       <c r="R28" s="47" t="n"/>
       <c r="T28" s="50">
-        <f>IF(J28="","",0.05)</f>
+        <f>IF(A28="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       <c r="Q29" s="47" t="n"/>
       <c r="R29" s="47" t="n"/>
       <c r="T29" s="50">
-        <f>IF(J29="","",0.05)</f>
+        <f>IF(A29="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       <c r="Q30" s="47" t="n"/>
       <c r="R30" s="47" t="n"/>
       <c r="T30" s="50">
-        <f>IF(J30="","",0.05)</f>
+        <f>IF(A30="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="Q31" s="47" t="n"/>
       <c r="R31" s="47" t="n"/>
       <c r="T31" s="50">
-        <f>IF(J31="","",0.05)</f>
+        <f>IF(A31="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       <c r="Q32" s="47" t="n"/>
       <c r="R32" s="47" t="n"/>
       <c r="T32" s="50">
-        <f>IF(J32="","",0.05)</f>
+        <f>IF(A32="","",$B$8)</f>
         <v/>
       </c>
     </row>
@@ -2124,19 +2124,19 @@
       <c r="Q33" s="47" t="n"/>
       <c r="R33" s="47" t="n"/>
       <c r="T33" s="50">
-        <f>IF(J33="","",0.05)</f>
+        <f>IF(A33="","",$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="T34" s="50">
-        <f>IF(J34="","",0.05)</f>
+        <f>IF(A34="","",$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="T35" s="50">
-        <f>IF(J35="","",0.05)</f>
+        <f>IF(A35="","",$B$8)</f>
         <v/>
       </c>
     </row>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -677,9 +677,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>21</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7200000" cy="3240000"/>
@@ -1019,6 +1019,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="24">
       <c r="A4" s="32" t="inlineStr">
         <is>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -631,8 +631,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -252,7 +252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -418,6 +418,9 @@
     </xf>
     <xf numFmtId="164" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1078,10 +1081,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1" s="24">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>BEFORE EVERY TEST:  stratify first  ·  check independence  ·  declare the practical threshold  ·  plot the data</t>
+    <row r="9" ht="48" customHeight="1" s="24">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>BEFORE EVERY TEST:  stratify first  ·  check independence  ·  declare the practical threshold  ·  plot the data  ·  Key: p-value = the chance of seeing a difference this big if nothing had really changed · Effect size = how big the difference is, in units a manager can act on · CI = confidence interval, the range the true value plausibly sits in</t>
         </is>
       </c>
     </row>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1611,7 +1611,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="24">
-      <c r="A16" s="46" t="n">
+      <c r="A16" s="51" t="n">
         <v>6</v>
       </c>
       <c r="B16" s="47" t="n"/>
@@ -1640,7 +1640,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="24">
-      <c r="A17" s="46" t="n">
+      <c r="A17" s="51" t="n">
         <v>7</v>
       </c>
       <c r="B17" s="47" t="n"/>
@@ -1669,7 +1669,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="24">
-      <c r="A18" s="46" t="n">
+      <c r="A18" s="51" t="n">
         <v>8</v>
       </c>
       <c r="B18" s="47" t="n"/>
@@ -1698,7 +1698,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="24">
-      <c r="A19" s="46" t="n">
+      <c r="A19" s="51" t="n">
         <v>9</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1727,7 +1727,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="24">
-      <c r="A20" s="46" t="n">
+      <c r="A20" s="51" t="n">
         <v>10</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1756,7 +1756,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="24">
-      <c r="A21" s="46" t="n">
+      <c r="A21" s="51" t="n">
         <v>11</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1785,7 +1785,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="24">
-      <c r="A22" s="46" t="n">
+      <c r="A22" s="51" t="n">
         <v>12</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1814,7 +1814,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="24">
-      <c r="A23" s="46" t="n">
+      <c r="A23" s="51" t="n">
         <v>13</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1843,7 +1843,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="24">
-      <c r="A24" s="46" t="n">
+      <c r="A24" s="51" t="n">
         <v>14</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1872,7 +1872,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="24">
-      <c r="A25" s="46" t="n">
+      <c r="A25" s="51" t="n">
         <v>15</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1901,7 +1901,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="24">
-      <c r="A26" s="46" t="n">
+      <c r="A26" s="51" t="n">
         <v>16</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="24">
-      <c r="A27" s="46" t="n">
+      <c r="A27" s="51" t="n">
         <v>17</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="24">
-      <c r="A28" s="46" t="n">
+      <c r="A28" s="51" t="n">
         <v>18</v>
       </c>
       <c r="B28" s="47" t="n"/>
@@ -1988,7 +1988,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="24">
-      <c r="A29" s="46" t="n">
+      <c r="A29" s="51" t="n">
         <v>19</v>
       </c>
       <c r="B29" s="47" t="n"/>
@@ -2017,7 +2017,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="24">
-      <c r="A30" s="46" t="n">
+      <c r="A30" s="51" t="n">
         <v>20</v>
       </c>
       <c r="B30" s="47" t="n"/>
@@ -2046,7 +2046,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="24">
-      <c r="A31" s="46" t="n">
+      <c r="A31" s="51" t="n">
         <v>21</v>
       </c>
       <c r="B31" s="47" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="24">
-      <c r="A32" s="46" t="n">
+      <c r="A32" s="51" t="n">
         <v>22</v>
       </c>
       <c r="B32" s="47" t="n"/>
@@ -2104,7 +2104,7 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="24">
-      <c r="A33" s="46" t="n">
+      <c r="A33" s="51" t="n">
         <v>23</v>
       </c>
       <c r="B33" s="47" t="n"/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
-          <t>Used by the 'Above threshold?' column. 0.05 is standard; drop to 0.01 when acting on the result is expensive.</t>
+          <t>Used by the 'Above threshold?' column. 0.05 is standard; drop to 0.01 when acting on the result is expensive. WHICH TEST GOES IN THE TEST COLUMN — the log never named one, and eight tools in the library send you here. Two means, normal-ish: two-sample t-test. Two means, skewed (most support duration data): Mann-Whitney U. Before and after on the SAME units: paired t-test, or Wilcoxon signed-rank if skewed. Three or more groups: one-way ANOVA, or Kruskal-Wallis if skewed. Rates or proportions: one- and two-proportion tests. Two categorical variables: chi-square test of independence. Comparing spread rather than centre: Levene's test. Check the shape first on the 'Shape and spread' tab of 25-pareto-and-distribution.xlsx — it decides which half of that list you are in.</t>
         </is>
       </c>
     </row>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -252,7 +252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -421,6 +421,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1611,7 +1614,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="24">
-      <c r="A16" s="51" t="n">
+      <c r="A16" s="59" t="n">
         <v>6</v>
       </c>
       <c r="B16" s="47" t="n"/>
@@ -1640,7 +1643,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="24">
-      <c r="A17" s="51" t="n">
+      <c r="A17" s="59" t="n">
         <v>7</v>
       </c>
       <c r="B17" s="47" t="n"/>
@@ -1669,7 +1672,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="24">
-      <c r="A18" s="51" t="n">
+      <c r="A18" s="59" t="n">
         <v>8</v>
       </c>
       <c r="B18" s="47" t="n"/>
@@ -1698,7 +1701,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="24">
-      <c r="A19" s="51" t="n">
+      <c r="A19" s="59" t="n">
         <v>9</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1727,7 +1730,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="24">
-      <c r="A20" s="51" t="n">
+      <c r="A20" s="59" t="n">
         <v>10</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1756,7 +1759,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="24">
-      <c r="A21" s="51" t="n">
+      <c r="A21" s="59" t="n">
         <v>11</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1785,7 +1788,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="24">
-      <c r="A22" s="51" t="n">
+      <c r="A22" s="59" t="n">
         <v>12</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1814,7 +1817,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="24">
-      <c r="A23" s="51" t="n">
+      <c r="A23" s="59" t="n">
         <v>13</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1843,7 +1846,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="24">
-      <c r="A24" s="51" t="n">
+      <c r="A24" s="59" t="n">
         <v>14</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1872,7 +1875,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="24">
-      <c r="A25" s="51" t="n">
+      <c r="A25" s="59" t="n">
         <v>15</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1901,7 +1904,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="24">
-      <c r="A26" s="51" t="n">
+      <c r="A26" s="59" t="n">
         <v>16</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1930,7 +1933,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="24">
-      <c r="A27" s="51" t="n">
+      <c r="A27" s="59" t="n">
         <v>17</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1959,7 +1962,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="24">
-      <c r="A28" s="51" t="n">
+      <c r="A28" s="59" t="n">
         <v>18</v>
       </c>
       <c r="B28" s="47" t="n"/>
@@ -1988,7 +1991,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="24">
-      <c r="A29" s="51" t="n">
+      <c r="A29" s="59" t="n">
         <v>19</v>
       </c>
       <c r="B29" s="47" t="n"/>
@@ -2017,7 +2020,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="24">
-      <c r="A30" s="51" t="n">
+      <c r="A30" s="59" t="n">
         <v>20</v>
       </c>
       <c r="B30" s="47" t="n"/>
@@ -2046,7 +2049,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="24">
-      <c r="A31" s="51" t="n">
+      <c r="A31" s="59" t="n">
         <v>21</v>
       </c>
       <c r="B31" s="47" t="n"/>
@@ -2075,7 +2078,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="24">
-      <c r="A32" s="51" t="n">
+      <c r="A32" s="59" t="n">
         <v>22</v>
       </c>
       <c r="B32" s="47" t="n"/>
@@ -2104,7 +2107,7 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="24">
-      <c r="A33" s="51" t="n">
+      <c r="A33" s="59" t="n">
         <v>23</v>
       </c>
       <c r="B33" s="47" t="n"/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1614,7 +1614,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="24">
-      <c r="A16" s="59" t="n">
+      <c r="A16" s="51" t="n">
         <v>6</v>
       </c>
       <c r="B16" s="47" t="n"/>
@@ -1643,7 +1643,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="24">
-      <c r="A17" s="59" t="n">
+      <c r="A17" s="51" t="n">
         <v>7</v>
       </c>
       <c r="B17" s="47" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="24">
-      <c r="A18" s="59" t="n">
+      <c r="A18" s="51" t="n">
         <v>8</v>
       </c>
       <c r="B18" s="47" t="n"/>
@@ -1701,7 +1701,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="24">
-      <c r="A19" s="59" t="n">
+      <c r="A19" s="51" t="n">
         <v>9</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1730,7 +1730,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="24">
-      <c r="A20" s="59" t="n">
+      <c r="A20" s="51" t="n">
         <v>10</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="24">
-      <c r="A21" s="59" t="n">
+      <c r="A21" s="51" t="n">
         <v>11</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1788,7 +1788,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="24">
-      <c r="A22" s="59" t="n">
+      <c r="A22" s="51" t="n">
         <v>12</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1817,7 +1817,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="24">
-      <c r="A23" s="59" t="n">
+      <c r="A23" s="51" t="n">
         <v>13</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1846,7 +1846,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="24">
-      <c r="A24" s="59" t="n">
+      <c r="A24" s="51" t="n">
         <v>14</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1875,7 +1875,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="24">
-      <c r="A25" s="59" t="n">
+      <c r="A25" s="51" t="n">
         <v>15</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1904,7 +1904,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="24">
-      <c r="A26" s="59" t="n">
+      <c r="A26" s="51" t="n">
         <v>16</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1933,7 +1933,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="24">
-      <c r="A27" s="59" t="n">
+      <c r="A27" s="51" t="n">
         <v>17</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1962,7 +1962,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="24">
-      <c r="A28" s="59" t="n">
+      <c r="A28" s="51" t="n">
         <v>18</v>
       </c>
       <c r="B28" s="47" t="n"/>
@@ -1991,7 +1991,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="24">
-      <c r="A29" s="59" t="n">
+      <c r="A29" s="51" t="n">
         <v>19</v>
       </c>
       <c r="B29" s="47" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="24">
-      <c r="A30" s="59" t="n">
+      <c r="A30" s="51" t="n">
         <v>20</v>
       </c>
       <c r="B30" s="47" t="n"/>
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="24">
-      <c r="A31" s="59" t="n">
+      <c r="A31" s="51" t="n">
         <v>21</v>
       </c>
       <c r="B31" s="47" t="n"/>
@@ -2078,7 +2078,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="24">
-      <c r="A32" s="59" t="n">
+      <c r="A32" s="51" t="n">
         <v>22</v>
       </c>
       <c r="B32" s="47" t="n"/>
@@ -2107,7 +2107,7 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="24">
-      <c r="A33" s="59" t="n">
+      <c r="A33" s="51" t="n">
         <v>23</v>
       </c>
       <c r="B33" s="47" t="n"/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -252,7 +252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -424,6 +424,24 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1060,12 +1078,12 @@
     <row r="7" ht="15" customHeight="1" s="24">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1632,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="24">
-      <c r="A16" s="51" t="n">
+      <c r="A16" s="59" t="n">
         <v>6</v>
       </c>
       <c r="B16" s="47" t="n"/>
@@ -1643,7 +1661,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="24">
-      <c r="A17" s="51" t="n">
+      <c r="A17" s="59" t="n">
         <v>7</v>
       </c>
       <c r="B17" s="47" t="n"/>
@@ -1672,7 +1690,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="24">
-      <c r="A18" s="51" t="n">
+      <c r="A18" s="59" t="n">
         <v>8</v>
       </c>
       <c r="B18" s="47" t="n"/>
@@ -1701,7 +1719,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="24">
-      <c r="A19" s="51" t="n">
+      <c r="A19" s="59" t="n">
         <v>9</v>
       </c>
       <c r="B19" s="47" t="n"/>
@@ -1730,7 +1748,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="24">
-      <c r="A20" s="51" t="n">
+      <c r="A20" s="59" t="n">
         <v>10</v>
       </c>
       <c r="B20" s="47" t="n"/>
@@ -1759,7 +1777,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="24">
-      <c r="A21" s="51" t="n">
+      <c r="A21" s="59" t="n">
         <v>11</v>
       </c>
       <c r="B21" s="47" t="n"/>
@@ -1788,7 +1806,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="24">
-      <c r="A22" s="51" t="n">
+      <c r="A22" s="59" t="n">
         <v>12</v>
       </c>
       <c r="B22" s="47" t="n"/>
@@ -1817,7 +1835,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="24">
-      <c r="A23" s="51" t="n">
+      <c r="A23" s="59" t="n">
         <v>13</v>
       </c>
       <c r="B23" s="47" t="n"/>
@@ -1846,7 +1864,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="24">
-      <c r="A24" s="51" t="n">
+      <c r="A24" s="59" t="n">
         <v>14</v>
       </c>
       <c r="B24" s="47" t="n"/>
@@ -1875,7 +1893,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="24">
-      <c r="A25" s="51" t="n">
+      <c r="A25" s="59" t="n">
         <v>15</v>
       </c>
       <c r="B25" s="47" t="n"/>
@@ -1904,7 +1922,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="24">
-      <c r="A26" s="51" t="n">
+      <c r="A26" s="59" t="n">
         <v>16</v>
       </c>
       <c r="B26" s="47" t="n"/>
@@ -1933,7 +1951,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="24">
-      <c r="A27" s="51" t="n">
+      <c r="A27" s="59" t="n">
         <v>17</v>
       </c>
       <c r="B27" s="47" t="n"/>
@@ -1962,7 +1980,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="24">
-      <c r="A28" s="51" t="n">
+      <c r="A28" s="59" t="n">
         <v>18</v>
       </c>
       <c r="B28" s="47" t="n"/>
@@ -1991,7 +2009,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="24">
-      <c r="A29" s="51" t="n">
+      <c r="A29" s="59" t="n">
         <v>19</v>
       </c>
       <c r="B29" s="47" t="n"/>
@@ -2020,7 +2038,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="24">
-      <c r="A30" s="51" t="n">
+      <c r="A30" s="59" t="n">
         <v>20</v>
       </c>
       <c r="B30" s="47" t="n"/>
@@ -2049,7 +2067,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="24">
-      <c r="A31" s="51" t="n">
+      <c r="A31" s="59" t="n">
         <v>21</v>
       </c>
       <c r="B31" s="47" t="n"/>
@@ -2078,7 +2096,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="24">
-      <c r="A32" s="51" t="n">
+      <c r="A32" s="59" t="n">
         <v>22</v>
       </c>
       <c r="B32" s="47" t="n"/>
@@ -2107,7 +2125,7 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="24">
-      <c r="A33" s="51" t="n">
+      <c r="A33" s="59" t="n">
         <v>23</v>
       </c>
       <c r="B33" s="47" t="n"/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -252,7 +252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -442,6 +442,9 @@
     </xf>
     <xf numFmtId="164" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1024,9 +1027,24 @@
   <cols>
     <col width="38" customWidth="1" style="23" min="1" max="1"/>
     <col width="22" customWidth="1" style="23" min="2" max="3"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
     <col width="50" customWidth="1" style="23" min="4" max="4"/>
     <col width="12" customWidth="1" style="23" min="5" max="5"/>
     <col width="4" customWidth="1" style="23" min="6" max="18"/>
+    <col width="13" customWidth="1" style="24" min="7" max="7"/>
+    <col width="13" customWidth="1" style="24" min="8" max="8"/>
+    <col width="13" customWidth="1" style="24" min="9" max="9"/>
+    <col width="13" customWidth="1" style="24" min="10" max="10"/>
+    <col width="13" customWidth="1" style="24" min="11" max="11"/>
+    <col width="13" customWidth="1" style="24" min="12" max="12"/>
+    <col width="13" customWidth="1" style="24" min="13" max="13"/>
+    <col width="13" customWidth="1" style="24" min="14" max="14"/>
+    <col width="13" customWidth="1" style="24" min="15" max="15"/>
+    <col width="13" customWidth="1" style="24" min="16" max="16"/>
+    <col width="13" customWidth="1" style="24" min="17" max="17"/>
+    <col width="13" customWidth="1" style="24" min="18" max="18"/>
+    <col width="13" customWidth="1" style="24" min="19" max="19"/>
+    <col width="13" customWidth="1" style="24" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="24">
@@ -1087,7 +1105,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="52" customHeight="1" s="24">
       <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Significance level (alpha)</t>
@@ -1096,7 +1114,7 @@
       <c r="B8" s="38" t="n">
         <v>0.05</v>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>Used by the 'Above threshold?' column. 0.05 is standard; drop to 0.01 when acting on the result is expensive. WHICH TEST GOES IN THE TEST COLUMN — the log never named one, and eight tools in the library send you here. Two means, normal-ish: two-sample t-test. Two means, skewed (most support duration data): Mann-Whitney U. Before and after on the SAME units: paired t-test, or Wilcoxon signed-rank if skewed. Three or more groups: one-way ANOVA, or Kruskal-Wallis if skewed. Rates or proportions: one- and two-proportion tests. Two categorical variables: chi-square test of independence. Comparing spread rather than centre: Levene's test. Check the shape first on the 'Shape and spread' tab of 25-pareto-and-distribution.xlsx — it decides which half of that list you are in.</t>
         </is>
@@ -2269,7 +2287,7 @@
       <c r="E45" s="47" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A2:R2"/>
@@ -2278,6 +2296,7 @@
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A9:R9"/>
+    <mergeCell ref="C8:T8"/>
   </mergeCells>
   <conditionalFormatting sqref="N11:N33">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1120,10 +1120,16 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" s="24">
+    <row r="9" ht="96" customHeight="1" s="24">
       <c r="A9" s="58" t="inlineStr">
         <is>
-          <t>BEFORE EVERY TEST:  stratify first  ·  check independence  ·  declare the practical threshold  ·  plot the data  ·  Key: p-value = the chance of seeing a difference this big if nothing had really changed · Effect size = how big the difference is, in units a manager can act on · CI = confidence interval, the range the true value plausibly sits in</t>
+          <t>BEFORE EVERY TEST:  stratify first  ·  check independence  ·  declare the practical threshold  ·  plot the data  ·  Key:
+• p-value = the chance of seeing a difference this big if nothing had really changed
+• Effect size = how big the difference is, in units a manager can act on
+• CI = confidence interval, the range the true value plausibly sits in  ·  Key:
+• p-value = the chance of seeing a difference this big if nothing had really changed
+• Effect size = how big the difference is, in units a manager can act on
+• CI = confidence interval, the range the true value plausibly sits in</t>
         </is>
       </c>
     </row>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -152,6 +152,11 @@
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -252,7 +257,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -444,6 +449,9 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1022,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="23" min="1" max="1"/>
@@ -1045,6 +1053,14 @@
     <col width="13" customWidth="1" style="24" min="18" max="18"/>
     <col width="13" customWidth="1" style="24" min="19" max="19"/>
     <col width="13" customWidth="1" style="24" min="20" max="20"/>
+    <col width="13" customWidth="1" style="24" min="21" max="21"/>
+    <col width="13" customWidth="1" style="24" min="22" max="22"/>
+    <col width="13" customWidth="1" style="24" min="23" max="23"/>
+    <col width="13" customWidth="1" style="24" min="24" max="24"/>
+    <col width="13" customWidth="1" style="24" min="25" max="25"/>
+    <col width="13" customWidth="1" style="24" min="26" max="26"/>
+    <col width="13" customWidth="1" style="24" min="27" max="27"/>
+    <col width="13" customWidth="1" style="24" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="24">
@@ -1120,10 +1136,16 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="96" customHeight="1" s="24">
+    <row r="9" ht="168" customHeight="1" s="24">
       <c r="A9" s="58" t="inlineStr">
         <is>
           <t>BEFORE EVERY TEST:  stratify first  ·  check independence  ·  declare the practical threshold  ·  plot the data  ·  Key:
+• p-value = the chance of seeing a difference this big if nothing had really changed
+• Effect size = how big the difference is, in units a manager can act on
+• CI = confidence interval, the range the true value plausibly sits in  ·  Key:
+• p-value = the chance of seeing a difference this big if nothing had really changed
+• Effect size = how big the difference is, in units a manager can act on
+• CI = confidence interval, the range the true value plausibly sits in  ·  Key:
 • p-value = the chance of seeing a difference this big if nothing had really changed
 • Effect size = how big the difference is, in units a manager can act on
 • CI = confidence interval, the range the true value plausibly sits in  ·  Key:
@@ -2189,10 +2211,16 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="19.5" customHeight="1" s="24">
+    <row r="36" ht="66" customHeight="1" s="24">
       <c r="A36" s="32" t="inlineStr">
         <is>
           <t>TESTS RUN AND REJECTED  —  record these so nobody re-litigates them in month five</t>
+        </is>
+      </c>
+      <c r="T36" s="67" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  The line is your alpha, not a verdict. A p-value below it says the difference is unlikely to be noise — it says nothing about whether the difference is worth acting on, which is what the practical threshold you registered beforehand is for. Watch for a wall of tests just under the line: that is the shape of hypothesis-shopping.
+SO:  Act only where the result clears the practical threshold you registered before the test. A p-value under the line with an effect below that threshold is a finding you should record and not fund.</t>
         </is>
       </c>
     </row>
@@ -2293,11 +2321,12 @@
       <c r="E45" s="47" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="T36:AB36"/>
     <mergeCell ref="A36:R36"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:F4"/>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1136,19 +1136,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="168" customHeight="1" s="24">
+    <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="58" t="inlineStr">
         <is>
           <t>BEFORE EVERY TEST:  stratify first  ·  check independence  ·  declare the practical threshold  ·  plot the data  ·  Key:
-• p-value = the chance of seeing a difference this big if nothing had really changed
-• Effect size = how big the difference is, in units a manager can act on
-• CI = confidence interval, the range the true value plausibly sits in  ·  Key:
-• p-value = the chance of seeing a difference this big if nothing had really changed
-• Effect size = how big the difference is, in units a manager can act on
-• CI = confidence interval, the range the true value plausibly sits in  ·  Key:
-• p-value = the chance of seeing a difference this big if nothing had really changed
-• Effect size = how big the difference is, in units a manager can act on
-• CI = confidence interval, the range the true value plausibly sits in  ·  Key:
 • p-value = the chance of seeing a difference this big if nothing had really changed
 • Effect size = how big the difference is, in units a manager can act on
 • CI = confidence interval, the range the true value plausibly sits in</t>

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -570,7 +570,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>p-value by test, against alpha = 0.05</a:t>
+              <a:t>p-value by test — anything under the alpha line is a real difference</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -621,7 +621,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>alpha (0.05)</v>
+            <v>alpha — the value in B8</v>
           </tx>
           <spPr>
             <a:ln w="16000">
@@ -1237,10 +1237,9 @@
           <t>Analyst</t>
         </is>
       </c>
-      <c r="T10" s="37" t="inlineStr">
-        <is>
-          <t>alpha</t>
-        </is>
+      <c r="T10" s="37">
+        <f>IF($B$8="","alpha","alpha ("&amp;TEXT($B$8,"0.###")&amp;")")</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="348.5" customHeight="1" s="24">

--- a/templates/13-hypothesis-test-log.xlsx
+++ b/templates/13-hypothesis-test-log.xlsx
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M11" s="52" t="inlineStr">
         <is>
-          <t>1.5 pts</t>
+          <t>13.1 pts</t>
         </is>
       </c>
       <c r="N11" s="45">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="O11" s="52" t="inlineStr">
         <is>
-          <t>Reopens fell 4.9 points, well past the 1.5 we agreed mattered</t>
+          <t>Reopens fell 4.9 points — real, and short of the 13.1 points registered as the smallest change that clears the floor. Significant is not the same as bookable</t>
         </is>
       </c>
       <c r="P11" s="52" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="Q11" s="52" t="inlineStr">
